--- a/volunteer_registration_forms/047_volunteer_signup_form--volunteer_registration_forms.xlsx
+++ b/volunteer_registration_forms/047_volunteer_signup_form--volunteer_registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -942,8 +942,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -971,12 +971,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'chatjimmy',_'label':_'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'chatjimmy', 'label': 'ChatJimmy'}</t>
+          <t>ChatJimmy</t>
         </is>
       </c>
     </row>
@@ -988,12 +988,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'tool2',_'label':_'tool_2'}</t>
+          <t>tool_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'tool2', 'label': 'Tool 2'}</t>
+          <t>Tool 2</t>
         </is>
       </c>
     </row>
@@ -1005,12 +1005,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'tool3',_'label':_'tool_3'}</t>
+          <t>tool_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'tool3', 'label': 'Tool 3'}</t>
+          <t>Tool 3</t>
         </is>
       </c>
     </row>
@@ -1022,12 +1022,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'project1',_'label':_'project_1'}</t>
+          <t>project_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'project1', 'label': 'Project 1'}</t>
+          <t>Project 1</t>
         </is>
       </c>
     </row>
@@ -1039,12 +1039,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'project2',_'label':_'project_2'}</t>
+          <t>project_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'project2', 'label': 'Project 2'}</t>
+          <t>Project 2</t>
         </is>
       </c>
     </row>
@@ -1056,12 +1056,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_6,_'name':_'project3',_'label':_'project_3'}</t>
+          <t>project_3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 6, 'name': 'project3', 'label': 'Project 3'}</t>
+          <t>Project 3</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_7,_'name':_'task1',_'label':_'task_1'}</t>
+          <t>task_1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 7, 'name': 'task1', 'label': 'Task 1'}</t>
+          <t>Task 1</t>
         </is>
       </c>
     </row>
@@ -1090,12 +1090,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_8,_'name':_'task2',_'label':_'task_2'}</t>
+          <t>task_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 8, 'name': 'task2', 'label': 'Task 2'}</t>
+          <t>Task 2</t>
         </is>
       </c>
     </row>
@@ -1107,12 +1107,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_9,_'name':_'task3',_'label':_'task_3'}</t>
+          <t>task_3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 9, 'name': 'task3', 'label': 'Task 3'}</t>
+          <t>Task 3</t>
         </is>
       </c>
     </row>
@@ -1124,12 +1124,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_10,_'name':_'nationality1',_'label':_'nationality_1'}</t>
+          <t>nationality_1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 10, 'name': 'nationality1', 'label': 'Nationality 1'}</t>
+          <t>Nationality 1</t>
         </is>
       </c>
     </row>
@@ -1141,12 +1141,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_11,_'name':_'nationality2',_'label':_'nationality_2'}</t>
+          <t>nationality_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 11, 'name': 'nationality2', 'label': 'Nationality 2'}</t>
+          <t>Nationality 2</t>
         </is>
       </c>
     </row>
@@ -1158,12 +1158,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_12,_'name':_'nationality3',_'label':_'nationality_3'}</t>
+          <t>nationality_3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 12, 'name': 'nationality3', 'label': 'Nationality 3'}</t>
+          <t>Nationality 3</t>
         </is>
       </c>
     </row>
@@ -1175,12 +1175,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_13,_'name':_'language1',_'label':_'language_1'}</t>
+          <t>language_1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 13, 'name': 'language1', 'label': 'Language 1'}</t>
+          <t>Language 1</t>
         </is>
       </c>
     </row>
@@ -1192,12 +1192,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_14,_'name':_'language2',_'label':_'language_2'}</t>
+          <t>language_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 14, 'name': 'language2', 'label': 'Language 2'}</t>
+          <t>Language 2</t>
         </is>
       </c>
     </row>
@@ -1209,12 +1209,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_15,_'name':_'language3',_'label':_'language_3'}</t>
+          <t>language_3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 15, 'name': 'language3', 'label': 'Language 3'}</t>
+          <t>Language 3</t>
         </is>
       </c>
     </row>
@@ -1226,12 +1226,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_16,_'name':_'role1',_'label':_'role_1'}</t>
+          <t>role_1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 16, 'name': 'role1', 'label': 'Role 1'}</t>
+          <t>Role 1</t>
         </is>
       </c>
     </row>
@@ -1243,12 +1243,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_17,_'name':_'role2',_'label':_'role_2'}</t>
+          <t>role_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 17, 'name': 'role2', 'label': 'Role 2'}</t>
+          <t>Role 2</t>
         </is>
       </c>
     </row>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_18,_'name':_'role3',_'label':_'role_3'}</t>
+          <t>role_3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 18, 'name': 'role3', 'label': 'Role 3'}</t>
+          <t>Role 3</t>
         </is>
       </c>
     </row>
